--- a/Data/FlightPlan/FPL_05OCT26.xlsx
+++ b/Data/FlightPlan/FPL_05OCT26.xlsx
@@ -719,7 +719,7 @@
     <t>06:45</t>
   </si>
   <si>
-    <t>09:44</t>
+    <t>09:48</t>
   </si>
   <si>
     <t>12:25</t>
@@ -728,6 +728,9 @@
     <t>VN-A630</t>
   </si>
   <si>
+    <t>10:01</t>
+  </si>
+  <si>
     <t>11:05</t>
   </si>
   <si>
@@ -767,6 +770,9 @@
     <t>06:50</t>
   </si>
   <si>
+    <t>06:27</t>
+  </si>
+  <si>
     <t>BMV</t>
   </si>
   <si>
@@ -818,90 +824,90 @@
     <t>SIN</t>
   </si>
   <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
     <t>16:30</t>
   </si>
   <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
     <t>VN-A643</t>
   </si>
   <si>
@@ -1235,7 +1241,7 @@
     <t>Total Record(s): 351</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 05, 2026 04:46</t>
+    <t xml:space="preserve">Generated on  Oct 05, 2026 05:03</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -6223,7 +6229,9 @@
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
-      <c r="M155" s="7"/>
+      <c t="s" r="M155" s="7">
+        <v>239</v>
+      </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
       <c t="s" r="A156" s="6">
@@ -6249,7 +6257,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>20</v>
@@ -6315,7 +6323,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>81</v>
@@ -6348,7 +6356,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>209</v>
@@ -6384,7 +6392,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6417,7 +6425,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6426,13 +6434,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>235</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6450,13 +6458,13 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>16</v>
@@ -6483,7 +6491,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6498,7 +6506,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6516,7 +6524,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6531,7 +6539,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6549,7 +6557,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6582,7 +6590,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6615,7 +6623,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6630,7 +6638,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6663,7 +6671,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6675,14 +6683,16 @@
         <v>109</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
-      <c r="M170" s="7"/>
+      <c t="s" r="M170" s="7">
+        <v>253</v>
+      </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
       <c t="s" r="A171" s="6">
@@ -6696,7 +6706,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6705,7 +6715,7 @@
         <v>109</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="I171" s="7">
         <v>132</v>
@@ -6729,22 +6739,22 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>109</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6762,7 +6772,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6795,7 +6805,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6807,7 +6817,7 @@
         <v>156</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>23</v>
@@ -6828,7 +6838,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6861,7 +6871,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6870,10 +6880,10 @@
         <v>35</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>163</v>
@@ -6894,22 +6904,22 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6942,7 +6952,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6954,7 +6964,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>182</v>
@@ -6975,7 +6985,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7008,7 +7018,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7023,7 +7033,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7041,7 +7051,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7053,7 +7063,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>65</v>
@@ -7074,7 +7084,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7083,10 +7093,10 @@
         <v>35</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>161</v>
@@ -7107,13 +7117,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>35</v>
@@ -7122,7 +7132,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7140,7 +7150,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7155,7 +7165,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7173,7 +7183,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7185,10 +7195,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7214,14 +7224,14 @@
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>887</v>
+        <v>811</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7230,13 +7240,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7247,45 +7257,63 @@
         <v>13</v>
       </c>
       <c r="B189" s="7">
-        <v>882</v>
+        <v>984</v>
       </c>
       <c t="s" r="C189" s="7">
         <v>14</v>
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>247</v>
+        <v>185</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c r="M189" s="7"/>
     </row>
     <row r="190" ht="15" customHeight="1">
-      <c r="A190" s="6"/>
-      <c r="B190" s="7"/>
-      <c r="C190" s="7"/>
+      <c t="s" r="A190" s="6">
+        <v>13</v>
+      </c>
+      <c r="B190" s="7">
+        <v>983</v>
+      </c>
+      <c t="s" r="C190" s="7">
+        <v>14</v>
+      </c>
       <c r="D190" s="7"/>
-      <c r="E190" s="7"/>
-      <c r="F190" s="7"/>
-      <c r="G190" s="8"/>
-      <c r="H190" s="8"/>
-      <c r="I190" s="7"/>
-      <c r="J190" s="7"/>
+      <c t="s" r="E190" s="7">
+        <v>269</v>
+      </c>
+      <c r="F190" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G190" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H190" s="8">
+        <v>270</v>
+      </c>
+      <c t="s" r="I190" s="7">
+        <v>168</v>
+      </c>
+      <c t="s" r="J190" s="7">
+        <v>272</v>
+      </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c r="M190" s="7"/>
@@ -7295,78 +7323,78 @@
         <v>13</v>
       </c>
       <c r="B191" s="7">
-        <v>703</v>
+        <v>812</v>
       </c>
       <c t="s" r="C191" s="7">
         <v>14</v>
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
+        <v>269</v>
+      </c>
+      <c r="F191" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G191" s="8">
         <v>270</v>
       </c>
-      <c r="F191" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G191" s="8">
-        <v>58</v>
-      </c>
       <c t="s" r="H191" s="8">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>271</v>
+        <v>150</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c r="M191" s="7"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
-      <c t="s" r="A192" s="6">
-        <v>13</v>
-      </c>
-      <c r="B192" s="7">
-        <v>704</v>
-      </c>
-      <c t="s" r="C192" s="7">
-        <v>14</v>
-      </c>
+      <c r="A192" s="6"/>
+      <c r="B192" s="7"/>
+      <c r="C192" s="7"/>
       <c r="D192" s="7"/>
-      <c t="s" r="E192" s="7">
-        <v>270</v>
-      </c>
-      <c r="F192" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G192" s="8">
-        <v>244</v>
-      </c>
-      <c t="s" r="H192" s="8">
-        <v>58</v>
-      </c>
-      <c t="s" r="I192" s="7">
-        <v>121</v>
-      </c>
-      <c t="s" r="J192" s="7">
-        <v>38</v>
-      </c>
+      <c r="E192" s="7"/>
+      <c r="F192" s="7"/>
+      <c r="G192" s="8"/>
+      <c r="H192" s="8"/>
+      <c r="I192" s="7"/>
+      <c r="J192" s="7"/>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c r="M192" s="7"/>
     </row>
     <row r="193" ht="14.25" customHeight="1">
-      <c r="A193" s="6"/>
-      <c r="B193" s="7"/>
-      <c r="C193" s="7"/>
+      <c t="s" r="A193" s="6">
+        <v>13</v>
+      </c>
+      <c r="B193" s="7">
+        <v>703</v>
+      </c>
+      <c t="s" r="C193" s="7">
+        <v>14</v>
+      </c>
       <c r="D193" s="7"/>
-      <c r="E193" s="7"/>
-      <c r="F193" s="7"/>
-      <c r="G193" s="8"/>
-      <c r="H193" s="8"/>
-      <c r="I193" s="7"/>
-      <c r="J193" s="7"/>
+      <c t="s" r="E193" s="7">
+        <v>273</v>
+      </c>
+      <c r="F193" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G193" s="8">
+        <v>58</v>
+      </c>
+      <c t="s" r="H193" s="8">
+        <v>245</v>
+      </c>
+      <c t="s" r="I193" s="7">
+        <v>274</v>
+      </c>
+      <c t="s" r="J193" s="7">
+        <v>90</v>
+      </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c r="M193" s="7"/>
@@ -7376,63 +7404,45 @@
         <v>13</v>
       </c>
       <c r="B194" s="7">
-        <v>447</v>
+        <v>704</v>
       </c>
       <c t="s" r="C194" s="7">
         <v>14</v>
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>16</v>
+        <v>245</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>214</v>
+        <v>121</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c r="M194" s="7"/>
     </row>
     <row r="195" ht="15" customHeight="1">
-      <c t="s" r="A195" s="6">
-        <v>13</v>
-      </c>
-      <c r="B195" s="7">
-        <v>440</v>
-      </c>
-      <c t="s" r="C195" s="7">
-        <v>14</v>
-      </c>
+      <c r="A195" s="6"/>
+      <c r="B195" s="7"/>
+      <c r="C195" s="7"/>
       <c r="D195" s="7"/>
-      <c t="s" r="E195" s="7">
-        <v>272</v>
-      </c>
-      <c r="F195" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G195" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H195" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I195" s="7">
-        <v>273</v>
-      </c>
-      <c t="s" r="J195" s="7">
-        <v>246</v>
-      </c>
+      <c r="E195" s="7"/>
+      <c r="F195" s="7"/>
+      <c r="G195" s="8"/>
+      <c r="H195" s="8"/>
+      <c r="I195" s="7"/>
+      <c r="J195" s="7"/>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c r="M195" s="7"/>
@@ -7442,14 +7452,14 @@
         <v>13</v>
       </c>
       <c r="B196" s="7">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7458,13 +7468,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>62</v>
+        <v>214</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7475,29 +7485,29 @@
         <v>13</v>
       </c>
       <c r="B197" s="7">
-        <v>408</v>
+        <v>440</v>
       </c>
       <c t="s" r="C197" s="7">
         <v>14</v>
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>113</v>
+        <v>276</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7508,14 +7518,14 @@
         <v>13</v>
       </c>
       <c r="B198" s="7">
-        <v>519</v>
+        <v>407</v>
       </c>
       <c t="s" r="C198" s="7">
         <v>14</v>
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7524,13 +7534,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>170</v>
+        <v>91</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7541,45 +7551,63 @@
         <v>13</v>
       </c>
       <c r="B199" s="7">
-        <v>522</v>
+        <v>408</v>
       </c>
       <c t="s" r="C199" s="7">
         <v>14</v>
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>274</v>
+        <v>113</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c r="M199" s="7"/>
     </row>
     <row r="200" ht="15" customHeight="1">
-      <c r="A200" s="6"/>
-      <c r="B200" s="7"/>
-      <c r="C200" s="7"/>
+      <c t="s" r="A200" s="6">
+        <v>13</v>
+      </c>
+      <c r="B200" s="7">
+        <v>519</v>
+      </c>
+      <c t="s" r="C200" s="7">
+        <v>14</v>
+      </c>
       <c r="D200" s="7"/>
-      <c r="E200" s="7"/>
-      <c r="F200" s="7"/>
-      <c r="G200" s="8"/>
-      <c r="H200" s="8"/>
-      <c r="I200" s="7"/>
-      <c r="J200" s="7"/>
+      <c t="s" r="E200" s="7">
+        <v>275</v>
+      </c>
+      <c r="F200" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G200" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H200" s="8">
+        <v>58</v>
+      </c>
+      <c t="s" r="I200" s="7">
+        <v>26</v>
+      </c>
+      <c t="s" r="J200" s="7">
+        <v>170</v>
+      </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c r="M200" s="7"/>
@@ -7589,7 +7617,7 @@
         <v>13</v>
       </c>
       <c r="B201" s="7">
-        <v>449</v>
+        <v>522</v>
       </c>
       <c t="s" r="C201" s="7">
         <v>14</v>
@@ -7602,50 +7630,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>276</v>
+        <v>224</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c r="M201" s="7"/>
     </row>
     <row r="202" ht="14.25" customHeight="1">
-      <c t="s" r="A202" s="6">
-        <v>13</v>
-      </c>
-      <c r="B202" s="7">
-        <v>450</v>
-      </c>
-      <c t="s" r="C202" s="7">
-        <v>14</v>
-      </c>
+      <c r="A202" s="6"/>
+      <c r="B202" s="7"/>
+      <c r="C202" s="7"/>
       <c r="D202" s="7"/>
-      <c t="s" r="E202" s="7">
-        <v>275</v>
-      </c>
-      <c r="F202" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G202" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H202" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I202" s="7">
-        <v>220</v>
-      </c>
-      <c t="s" r="J202" s="7">
-        <v>277</v>
-      </c>
+      <c r="E202" s="7"/>
+      <c r="F202" s="7"/>
+      <c r="G202" s="8"/>
+      <c r="H202" s="8"/>
+      <c r="I202" s="7"/>
+      <c r="J202" s="7"/>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c r="M202" s="7"/>
@@ -7655,14 +7665,14 @@
         <v>13</v>
       </c>
       <c r="B203" s="7">
-        <v>133</v>
+        <v>449</v>
       </c>
       <c t="s" r="C203" s="7">
         <v>14</v>
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7671,50 +7681,46 @@
         <v>16</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>145</v>
-      </c>
-      <c t="s" r="K203" s="7">
-        <v>278</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="K203" s="7"/>
       <c r="L203" s="7"/>
-      <c t="s" r="M203" s="7">
-        <v>62</v>
-      </c>
+      <c r="M203" s="7"/>
     </row>
     <row r="204" ht="14.25" customHeight="1">
       <c t="s" r="A204" s="6">
         <v>13</v>
       </c>
       <c r="B204" s="7">
-        <v>876</v>
+        <v>450</v>
       </c>
       <c t="s" r="C204" s="7">
         <v>14</v>
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>279</v>
+        <v>16</v>
       </c>
       <c t="s" r="I204" s="7">
+        <v>220</v>
+      </c>
+      <c t="s" r="J204" s="7">
         <v>280</v>
-      </c>
-      <c t="s" r="J204" s="7">
-        <v>187</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7725,47 +7731,51 @@
         <v>13</v>
       </c>
       <c r="B205" s="7">
-        <v>877</v>
+        <v>133</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>279</v>
+        <v>16</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c t="s" r="J205" s="7">
+        <v>145</v>
+      </c>
+      <c t="s" r="K205" s="7">
         <v>281</v>
       </c>
-      <c r="K205" s="7"/>
       <c r="L205" s="7"/>
-      <c r="M205" s="7"/>
+      <c t="s" r="M205" s="7">
+        <v>62</v>
+      </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c t="s" r="A206" s="6">
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>858</v>
+        <v>876</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7780,7 +7790,7 @@
         <v>283</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>284</v>
+        <v>187</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7788,17 +7798,17 @@
     </row>
     <row r="207" ht="14.25" customHeight="1">
       <c t="s" r="A207" s="6">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>859</v>
+        <v>877</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7810,92 +7820,92 @@
         <v>35</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>285</v>
+        <v>123</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c r="M207" s="7"/>
     </row>
     <row r="208" ht="14.25" customHeight="1">
-      <c r="A208" s="6"/>
-      <c r="B208" s="7"/>
-      <c r="C208" s="7"/>
+      <c t="s" r="A208" s="6">
+        <v>13</v>
+      </c>
+      <c r="B208" s="7">
+        <v>858</v>
+      </c>
+      <c t="s" r="C208" s="7">
+        <v>14</v>
+      </c>
       <c r="D208" s="7"/>
-      <c r="E208" s="7"/>
-      <c r="F208" s="7"/>
-      <c r="G208" s="8"/>
-      <c r="H208" s="8"/>
-      <c r="I208" s="7"/>
-      <c r="J208" s="7"/>
+      <c t="s" r="E208" s="7">
+        <v>278</v>
+      </c>
+      <c r="F208" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G208" s="8">
+        <v>35</v>
+      </c>
+      <c t="s" r="H208" s="8">
+        <v>285</v>
+      </c>
+      <c t="s" r="I208" s="7">
+        <v>286</v>
+      </c>
+      <c t="s" r="J208" s="7">
+        <v>287</v>
+      </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c r="M208" s="7"/>
     </row>
     <row r="209" ht="14.25" customHeight="1">
       <c t="s" r="A209" s="6">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="B209" s="7">
-        <v>809</v>
+        <v>859</v>
       </c>
       <c t="s" r="C209" s="7">
         <v>14</v>
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>35</v>
+        <v>285</v>
       </c>
       <c t="s" r="H209" s="8">
+        <v>35</v>
+      </c>
+      <c t="s" r="I209" s="7">
         <v>288</v>
       </c>
-      <c t="s" r="I209" s="7">
-        <v>118</v>
-      </c>
       <c t="s" r="J209" s="7">
-        <v>172</v>
+        <v>289</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c r="M209" s="7"/>
     </row>
     <row r="210" ht="15" customHeight="1">
-      <c t="s" r="A210" s="6">
-        <v>13</v>
-      </c>
-      <c r="B210" s="7">
-        <v>808</v>
-      </c>
-      <c t="s" r="C210" s="7">
-        <v>14</v>
-      </c>
+      <c r="A210" s="6"/>
+      <c r="B210" s="7"/>
+      <c r="C210" s="7"/>
       <c r="D210" s="7"/>
-      <c t="s" r="E210" s="7">
-        <v>287</v>
-      </c>
-      <c r="F210" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G210" s="8">
-        <v>288</v>
-      </c>
-      <c t="s" r="H210" s="8">
-        <v>35</v>
-      </c>
-      <c t="s" r="I210" s="7">
-        <v>221</v>
-      </c>
-      <c t="s" r="J210" s="7">
-        <v>145</v>
-      </c>
+      <c r="E210" s="7"/>
+      <c r="F210" s="7"/>
+      <c r="G210" s="8"/>
+      <c r="H210" s="8"/>
+      <c r="I210" s="7"/>
+      <c r="J210" s="7"/>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c r="M210" s="7"/>
@@ -7905,14 +7915,14 @@
         <v>13</v>
       </c>
       <c r="B211" s="7">
-        <v>144</v>
+        <v>809</v>
       </c>
       <c t="s" r="C211" s="7">
         <v>14</v>
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7921,13 +7931,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>16</v>
+        <v>291</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7938,29 +7948,29 @@
         <v>13</v>
       </c>
       <c r="B212" s="7">
-        <v>521</v>
+        <v>808</v>
       </c>
       <c t="s" r="C212" s="7">
         <v>14</v>
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>16</v>
+        <v>291</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7971,29 +7981,29 @@
         <v>13</v>
       </c>
       <c r="B213" s="7">
-        <v>518</v>
+        <v>144</v>
       </c>
       <c t="s" r="C213" s="7">
         <v>14</v>
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>289</v>
+        <v>138</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8004,14 +8014,14 @@
         <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>169</v>
+        <v>521</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8020,29 +8030,47 @@
         <v>16</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>290</v>
+        <v>205</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>291</v>
+        <v>28</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c r="M214" s="7"/>
     </row>
     <row r="215" ht="15" customHeight="1">
-      <c r="A215" s="6"/>
-      <c r="B215" s="7"/>
-      <c r="C215" s="7"/>
+      <c t="s" r="A215" s="6">
+        <v>13</v>
+      </c>
+      <c r="B215" s="7">
+        <v>518</v>
+      </c>
+      <c t="s" r="C215" s="7">
+        <v>14</v>
+      </c>
       <c r="D215" s="7"/>
-      <c r="E215" s="7"/>
-      <c r="F215" s="7"/>
-      <c r="G215" s="8"/>
-      <c r="H215" s="8"/>
-      <c r="I215" s="7"/>
-      <c r="J215" s="7"/>
+      <c t="s" r="E215" s="7">
+        <v>290</v>
+      </c>
+      <c r="F215" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G215" s="8">
+        <v>58</v>
+      </c>
+      <c t="s" r="H215" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I215" s="7">
+        <v>170</v>
+      </c>
+      <c t="s" r="J215" s="7">
+        <v>292</v>
+      </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c r="M215" s="7"/>
@@ -8052,14 +8080,14 @@
         <v>13</v>
       </c>
       <c r="B216" s="7">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c t="s" r="C216" s="7">
         <v>14</v>
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8081,34 +8109,16 @@
       <c r="M216" s="7"/>
     </row>
     <row r="217" ht="14.25" customHeight="1">
-      <c t="s" r="A217" s="6">
-        <v>13</v>
-      </c>
-      <c r="B217" s="7">
-        <v>811</v>
-      </c>
-      <c t="s" r="C217" s="7">
-        <v>14</v>
-      </c>
+      <c r="A217" s="6"/>
+      <c r="B217" s="7"/>
+      <c r="C217" s="7"/>
       <c r="D217" s="7"/>
-      <c t="s" r="E217" s="7">
-        <v>292</v>
-      </c>
-      <c r="F217" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G217" s="8">
-        <v>35</v>
-      </c>
-      <c t="s" r="H217" s="8">
-        <v>268</v>
-      </c>
-      <c t="s" r="I217" s="7">
-        <v>86</v>
-      </c>
-      <c t="s" r="J217" s="7">
-        <v>60</v>
-      </c>
+      <c r="E217" s="7"/>
+      <c r="F217" s="7"/>
+      <c r="G217" s="8"/>
+      <c r="H217" s="8"/>
+      <c r="I217" s="7"/>
+      <c r="J217" s="7"/>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c r="M217" s="7"/>
@@ -8118,29 +8128,29 @@
         <v>13</v>
       </c>
       <c r="B218" s="7">
-        <v>984</v>
+        <v>123</v>
       </c>
       <c t="s" r="C218" s="7">
         <v>14</v>
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>268</v>
+        <v>16</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>185</v>
+        <v>296</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8151,29 +8161,29 @@
         <v>13</v>
       </c>
       <c r="B219" s="7">
-        <v>983</v>
+        <v>887</v>
       </c>
       <c t="s" r="C219" s="7">
         <v>14</v>
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>168</v>
+        <v>46</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>296</v>
+        <v>120</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8184,29 +8194,29 @@
         <v>13</v>
       </c>
       <c r="B220" s="7">
-        <v>812</v>
+        <v>882</v>
       </c>
       <c t="s" r="C220" s="7">
         <v>14</v>
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>150</v>
+        <v>248</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>188</v>
+        <v>298</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8239,7 +8249,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8272,7 +8282,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8287,7 +8297,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8305,7 +8315,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8338,7 +8348,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8371,7 +8381,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8380,7 +8390,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="I226" s="7">
         <v>113</v>
@@ -8404,19 +8414,19 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>94</v>
@@ -8452,7 +8462,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8467,7 +8477,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8485,7 +8495,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8518,7 +8528,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8551,7 +8561,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8563,7 +8573,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>198</v>
@@ -8584,7 +8594,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8596,10 +8606,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8632,7 +8642,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8644,7 +8654,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>173</v>
@@ -8665,7 +8675,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8698,7 +8708,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8710,7 +8720,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>149</v>
@@ -8731,7 +8741,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8746,7 +8756,7 @@
         <v>161</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8764,7 +8774,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8776,7 +8786,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>96</v>
@@ -8797,7 +8807,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8845,7 +8855,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8857,7 +8867,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>102</v>
@@ -8878,7 +8888,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8890,7 +8900,7 @@
         <v>227</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>163</v>
@@ -8911,7 +8921,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8923,10 +8933,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8959,7 +8969,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -8971,7 +8981,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>153</v>
@@ -8992,7 +9002,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9004,10 +9014,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9025,7 +9035,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9058,7 +9068,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9091,7 +9101,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9106,7 +9116,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9139,7 +9149,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9172,7 +9182,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9205,7 +9215,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9217,10 +9227,10 @@
         <v>79</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9238,7 +9248,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9253,7 +9263,7 @@
         <v>203</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9271,7 +9281,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9304,7 +9314,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9316,10 +9326,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9352,7 +9362,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9361,7 +9371,7 @@
         <v>35</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>218</v>
@@ -9385,13 +9395,13 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>35</v>
@@ -9418,7 +9428,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9427,13 +9437,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>165</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9451,13 +9461,13 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>35</v>
@@ -9499,7 +9509,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -9514,7 +9524,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9532,7 +9542,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
@@ -9565,7 +9575,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
@@ -9580,7 +9590,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9613,7 +9623,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9646,7 +9656,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9661,7 +9671,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9679,7 +9689,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9691,7 +9701,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>159</v>
@@ -9712,7 +9722,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9745,7 +9755,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9793,13 +9803,13 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>35</v>
@@ -9826,7 +9836,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9838,10 +9848,10 @@
         <v>104</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9859,7 +9869,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9871,10 +9881,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9892,7 +9902,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -9940,7 +9950,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -9952,7 +9962,7 @@
         <v>166</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>45</v>
@@ -9973,7 +9983,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10006,7 +10016,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10039,7 +10049,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10072,7 +10082,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10081,7 +10091,7 @@
         <v>35</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="I283" s="7">
         <v>138</v>
@@ -10105,22 +10115,22 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10153,7 +10163,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10162,7 +10172,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="I286" s="7">
         <v>133</v>
@@ -10186,13 +10196,13 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>16</v>
@@ -10201,7 +10211,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10219,7 +10229,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10252,7 +10262,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10285,7 +10295,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10294,10 +10304,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>49</v>
@@ -10318,22 +10328,22 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10366,7 +10376,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10381,7 +10391,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10399,7 +10409,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10432,7 +10442,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10444,7 +10454,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>112</v>
@@ -10465,7 +10475,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10480,7 +10490,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10498,7 +10508,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10510,7 +10520,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>161</v>
@@ -10546,7 +10556,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10579,7 +10589,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10591,7 +10601,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J300" s="7">
         <v>65</v>
@@ -10612,7 +10622,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10624,10 +10634,10 @@
         <v>79</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10645,7 +10655,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10693,7 +10703,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10726,7 +10736,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10738,7 +10748,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>73</v>
@@ -10759,7 +10769,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -10771,7 +10781,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>80</v>
@@ -10792,7 +10802,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -10840,7 +10850,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -10849,7 +10859,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="I309" s="7">
         <v>87</v>
@@ -10873,13 +10883,13 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>16</v>
@@ -10888,7 +10898,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10906,7 +10916,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -10921,7 +10931,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10939,7 +10949,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -10954,7 +10964,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10972,7 +10982,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -10981,10 +10991,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>101</v>
@@ -11020,7 +11030,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11053,7 +11063,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11068,7 +11078,7 @@
         <v>168</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11086,7 +11096,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11095,13 +11105,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="I317" s="7">
         <v>82</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11119,13 +11129,13 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>35</v>
@@ -11152,7 +11162,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11164,7 +11174,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>49</v>
@@ -11185,7 +11195,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11194,10 +11204,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>77</v>
@@ -11233,7 +11243,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11245,15 +11255,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -11268,7 +11278,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -11301,7 +11311,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11334,7 +11344,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11343,10 +11353,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>216</v>
@@ -11367,22 +11377,22 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11400,7 +11410,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11412,7 +11422,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>182</v>
@@ -11448,7 +11458,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11481,7 +11491,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11496,7 +11506,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11514,7 +11524,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11529,7 +11539,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11547,7 +11557,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11559,10 +11569,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11595,7 +11605,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11607,10 +11617,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11628,7 +11638,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11661,7 +11671,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11673,7 +11683,7 @@
         <v>109</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>159</v>
@@ -11694,7 +11704,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11742,7 +11752,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11775,7 +11785,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -11808,7 +11818,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -11820,7 +11830,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>173</v>
@@ -11841,7 +11851,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -11874,7 +11884,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -11883,13 +11893,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>129</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11907,22 +11917,22 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11955,7 +11965,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -11988,7 +11998,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12021,7 +12031,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12036,7 +12046,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12054,7 +12064,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12087,7 +12097,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12096,13 +12106,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12120,22 +12130,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12168,7 +12178,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12201,7 +12211,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12213,7 +12223,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>195</v>
@@ -12234,7 +12244,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12267,7 +12277,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12300,7 +12310,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12309,7 +12319,7 @@
         <v>35</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="I357" s="7">
         <v>102</v>
@@ -12333,13 +12343,13 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>35</v>
@@ -12381,7 +12391,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12393,7 +12403,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>86</v>
@@ -12414,7 +12424,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12447,7 +12457,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12456,7 +12466,7 @@
         <v>58</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="I362" s="7">
         <v>75</v>
@@ -12480,19 +12490,19 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>39</v>
@@ -12513,7 +12523,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12522,13 +12532,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12546,22 +12556,22 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12594,7 +12604,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12606,10 +12616,10 @@
         <v>79</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12627,7 +12637,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12660,7 +12670,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12675,7 +12685,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12693,7 +12703,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12741,7 +12751,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12753,7 +12763,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>116</v>
@@ -12774,7 +12784,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12807,7 +12817,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12840,7 +12850,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -12852,7 +12862,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>53</v>
@@ -12873,7 +12883,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -12882,13 +12892,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12906,13 +12916,13 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>16</v>
@@ -12939,7 +12949,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -12951,10 +12961,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -12987,7 +12997,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -12996,7 +13006,7 @@
         <v>35</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="I380" s="7">
         <v>182</v>
@@ -13020,19 +13030,19 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>75</v>
@@ -13053,7 +13063,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13086,7 +13096,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13098,7 +13108,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>93</v>
@@ -13134,7 +13144,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13146,7 +13156,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>117</v>
@@ -13167,7 +13177,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13182,7 +13192,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13200,7 +13210,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13233,7 +13243,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13266,7 +13276,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13299,7 +13309,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13332,7 +13342,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13344,7 +13354,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>123</v>
@@ -13365,7 +13375,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13380,7 +13390,7 @@
         <v>188</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13398,7 +13408,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13413,7 +13423,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13442,11 +13452,11 @@
         <v>24</v>
       </c>
       <c t="s" r="C395" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -13494,7 +13504,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13527,7 +13537,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13539,7 +13549,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>28</v>
@@ -13560,7 +13570,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -13572,7 +13582,7 @@
         <v>184</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>190</v>
@@ -13608,7 +13618,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -13620,7 +13630,7 @@
         <v>156</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>118</v>
@@ -13641,7 +13651,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -13674,7 +13684,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13707,7 +13717,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13719,10 +13729,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13755,7 +13765,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
@@ -13767,7 +13777,7 @@
         <v>147</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>65</v>
@@ -13788,7 +13798,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
@@ -13800,7 +13810,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>205</v>
@@ -13821,7 +13831,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -13830,13 +13840,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13854,13 +13864,13 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>16</v>
@@ -13869,7 +13879,7 @@
         <v>211</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13902,19 +13912,19 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>136</v>
@@ -13935,7 +13945,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -13947,7 +13957,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>138</v>
@@ -13968,7 +13978,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -13977,13 +13987,13 @@
         <v>74</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>216</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14012,11 +14022,11 @@
         <v>606</v>
       </c>
       <c t="s" r="C415" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -14028,7 +14038,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>218</v>
@@ -14049,7 +14059,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -14058,7 +14068,7 @@
         <v>74</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="I416" s="7">
         <v>190</v>
@@ -14082,22 +14092,22 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14130,7 +14140,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
@@ -14145,7 +14155,7 @@
         <v>207</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14174,26 +14184,26 @@
         <v>35</v>
       </c>
       <c t="s" r="C421" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14226,7 +14236,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
@@ -14235,13 +14245,13 @@
         <v>74</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14259,13 +14269,13 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F424" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>74</v>
@@ -14274,7 +14284,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14307,7 +14317,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F426" s="7">
         <v>330</v>
@@ -14319,7 +14329,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J426" s="7">
         <v>123</v>
@@ -14336,11 +14346,11 @@
         <v>32</v>
       </c>
       <c t="s" r="C427" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F427" s="7">
         <v>330</v>
@@ -14349,13 +14359,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14388,7 +14398,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F429" s="7">
         <v>330</v>
@@ -14397,7 +14407,7 @@
         <v>35</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c t="s" r="I429" s="7">
         <v>46</v>
@@ -14421,22 +14431,22 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14469,7 +14479,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F432" s="7">
         <v>330</v>
@@ -14478,13 +14488,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H432" s="8">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c t="s" r="I432" s="7">
         <v>106</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -14502,22 +14512,22 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14525,7 +14535,7 @@
     </row>
     <row r="434" ht="15.75" customHeight="1">
       <c t="s" r="A434" s="9">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B434" s="9"/>
       <c r="C434" s="9"/>
@@ -14545,7 +14555,7 @@
     <row r="435" ht="66" customHeight="1"/>
     <row r="436" ht="16.5" customHeight="1">
       <c t="s" r="A436" s="10">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B436" s="10"/>
       <c r="C436" s="10"/>
@@ -14558,7 +14568,7 @@
       <c r="J436" s="10"/>
       <c r="K436" s="10"/>
       <c t="s" r="L436" s="11">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M436" s="11"/>
       <c r="N436" s="11"/>

--- a/Data/FlightPlan/FPL_05OCT26.xlsx
+++ b/Data/FlightPlan/FPL_05OCT26.xlsx
@@ -1001,6 +1001,9 @@
     <t>07:37</t>
   </si>
   <si>
+    <t>14:57</t>
+  </si>
+  <si>
     <t>16:30</t>
   </si>
   <si>
@@ -1076,6 +1079,9 @@
     <t>10:13</t>
   </si>
   <si>
+    <t>13:12</t>
+  </si>
+  <si>
     <t>VN-A648</t>
   </si>
   <si>
@@ -1196,168 +1202,171 @@
     <t>12:44</t>
   </si>
   <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>12:27</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>07:56</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>11:26</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>10:44</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>06:57</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>08:19</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>08:48</t>
+  </si>
+  <si>
+    <t>11:16</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:09</t>
+  </si>
+  <si>
+    <t>08:56</t>
+  </si>
+  <si>
+    <t>10:54</t>
+  </si>
+  <si>
+    <t>12:51</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>13:07</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>07:33</t>
+  </si>
+  <si>
+    <t>12:21</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
+    <t>VN-A693</t>
+  </si>
+  <si>
+    <t>15:23</t>
+  </si>
+  <si>
+    <t>VN-A697</t>
+  </si>
+  <si>
+    <t>VN-A699</t>
+  </si>
+  <si>
     <t>18:40</t>
   </si>
   <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>12:27</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>07:56</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>09:01</t>
-  </si>
-  <si>
-    <t>11:26</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>10:44</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>06:57</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>08:19</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>08:48</t>
-  </si>
-  <si>
-    <t>11:16</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:09</t>
-  </si>
-  <si>
-    <t>08:56</t>
-  </si>
-  <si>
-    <t>10:54</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>13:07</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
-    <t>07:33</t>
-  </si>
-  <si>
-    <t>12:21</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
-    <t>VN-A693</t>
-  </si>
-  <si>
-    <t>15:23</t>
-  </si>
-  <si>
-    <t>VN-A697</t>
-  </si>
-  <si>
-    <t>VN-A699</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
     <t>VN-A810</t>
   </si>
   <si>
@@ -1412,6 +1421,9 @@
     <t>MEL</t>
   </si>
   <si>
+    <t>00:07</t>
+  </si>
+  <si>
     <t>VN-A820</t>
   </si>
   <si>
@@ -1424,7 +1436,7 @@
     <t>Total Record(s): 350</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 05, 2026 11:24</t>
+    <t xml:space="preserve">Generated on  Oct 05, 2026 11:32</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -8484,7 +8496,9 @@
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
-      <c r="M219" s="7"/>
+      <c t="s" r="M219" s="7">
+        <v>330</v>
+      </c>
     </row>
     <row r="220" ht="15" customHeight="1">
       <c t="s" r="A220" s="6">
@@ -8513,7 +8527,7 @@
         <v>275</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8543,10 +8557,10 @@
         <v>116</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8576,10 +8590,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8612,7 +8626,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8632,7 +8646,7 @@
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8647,7 +8661,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8665,11 +8679,11 @@
         <v>284</v>
       </c>
       <c t="s" r="K225" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -8684,7 +8698,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8721,7 +8735,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8758,7 +8772,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8767,7 +8781,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="I228" s="7">
         <v>134</v>
@@ -8791,19 +8805,19 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>104</v>
@@ -8839,7 +8853,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8874,7 +8888,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8907,7 +8921,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8940,7 +8954,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8988,7 +9002,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9023,7 +9037,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9056,7 +9070,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9068,7 +9082,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>276</v>
@@ -9089,7 +9103,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9122,7 +9136,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9134,7 +9148,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>106</v>
@@ -9155,7 +9169,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9203,7 +9217,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9238,7 +9252,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9247,10 +9261,10 @@
         <v>36</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>185</v>
@@ -9271,22 +9285,22 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9319,7 +9333,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9331,7 +9345,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>174</v>
@@ -9339,7 +9353,7 @@
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9354,7 +9368,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9366,15 +9380,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9389,7 +9403,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9409,7 +9423,7 @@
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>83</v>
+        <v>356</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9424,7 +9438,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9457,7 +9471,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9472,7 +9486,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9505,7 +9519,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9525,7 +9539,7 @@
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9540,7 +9554,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9560,7 +9574,7 @@
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -9575,7 +9589,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9587,7 +9601,7 @@
         <v>88</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c t="s" r="J255" s="7">
         <v>20</v>
@@ -9610,7 +9624,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9643,7 +9657,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9676,7 +9690,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9688,10 +9702,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9724,7 +9738,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9744,7 +9758,7 @@
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -9759,7 +9773,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9779,7 +9793,7 @@
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -9809,7 +9823,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9829,7 +9843,7 @@
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -9844,7 +9858,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9864,7 +9878,7 @@
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -9879,7 +9893,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9912,7 +9926,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9945,7 +9959,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9993,13 +10007,13 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>36</v>
@@ -10028,7 +10042,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10061,7 +10075,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10076,7 +10090,7 @@
         <v>161</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -10094,7 +10108,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10142,7 +10156,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -10162,7 +10176,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10177,7 +10191,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -10210,7 +10224,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -10222,7 +10236,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>39</v>
@@ -10243,7 +10257,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -10276,7 +10290,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -10285,7 +10299,7 @@
         <v>36</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="I278" s="7">
         <v>160</v>
@@ -10309,19 +10323,19 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>278</v>
@@ -10357,7 +10371,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10392,7 +10406,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10425,7 +10439,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10458,7 +10472,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10491,7 +10505,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10500,7 +10514,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="I285" s="7">
         <v>296</v>
@@ -10524,13 +10538,13 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>16</v>
@@ -10539,7 +10553,7 @@
         <v>318</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10572,7 +10586,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10587,12 +10601,12 @@
         <v>140</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10607,7 +10621,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -10627,7 +10641,7 @@
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -10642,7 +10656,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -10675,7 +10689,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -10708,7 +10722,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10720,7 +10734,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>183</v>
@@ -10741,7 +10755,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10750,10 +10764,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>298</v>
@@ -10774,13 +10788,13 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>16</v>
@@ -10789,7 +10803,7 @@
         <v>239</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10822,7 +10836,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -10842,7 +10856,7 @@
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -10857,7 +10871,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -10890,7 +10904,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -10902,10 +10916,10 @@
         <v>88</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10923,7 +10937,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10971,7 +10985,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -11006,7 +11020,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -11041,7 +11055,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -11053,7 +11067,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>89</v>
@@ -11074,7 +11088,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -11107,7 +11121,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -11116,10 +11130,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>85</v>
@@ -11155,7 +11169,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11190,7 +11204,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11223,7 +11237,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -11256,7 +11270,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11271,7 +11285,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11289,7 +11303,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11298,10 +11312,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>111</v>
@@ -11337,7 +11351,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11359,7 +11373,7 @@
       </c>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11367,14 +11381,14 @@
         <v>13</v>
       </c>
       <c r="B314" s="7">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c t="s" r="C314" s="7">
         <v>14</v>
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11386,10 +11400,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>293</v>
+        <v>182</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11400,14 +11414,14 @@
         <v>13</v>
       </c>
       <c r="B315" s="7">
-        <v>640</v>
+        <v>146</v>
       </c>
       <c t="s" r="C315" s="7">
         <v>14</v>
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11416,50 +11430,46 @@
         <v>36</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>314</v>
+        <v>236</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="K315" s="7">
-        <v>41</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="K315" s="7"/>
       <c r="L315" s="7"/>
-      <c t="s" r="M315" s="7">
-        <v>236</v>
-      </c>
+      <c r="M315" s="7"/>
     </row>
     <row r="316" ht="14.25" customHeight="1">
       <c t="s" r="A316" s="6">
         <v>13</v>
       </c>
       <c r="B316" s="7">
-        <v>639</v>
+        <v>1127</v>
       </c>
       <c t="s" r="C316" s="7">
         <v>14</v>
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>25</v>
+        <v>397</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>395</v>
+        <v>226</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11470,14 +11480,14 @@
         <v>13</v>
       </c>
       <c r="B317" s="7">
-        <v>644</v>
+        <v>1128</v>
       </c>
       <c t="s" r="C317" s="7">
         <v>14</v>
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11486,47 +11496,29 @@
         <v>36</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>237</v>
+        <v>398</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>162</v>
+        <v>399</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c r="M317" s="7"/>
     </row>
     <row r="318" ht="14.25" customHeight="1">
-      <c t="s" r="A318" s="6">
-        <v>13</v>
-      </c>
-      <c r="B318" s="7">
-        <v>645</v>
-      </c>
-      <c t="s" r="C318" s="7">
-        <v>14</v>
-      </c>
+      <c r="A318" s="6"/>
+      <c r="B318" s="7"/>
+      <c r="C318" s="7"/>
       <c r="D318" s="7"/>
-      <c t="s" r="E318" s="7">
-        <v>393</v>
-      </c>
-      <c r="F318" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G318" s="8">
-        <v>64</v>
-      </c>
-      <c t="s" r="H318" s="8">
-        <v>36</v>
-      </c>
-      <c t="s" r="I318" s="7">
-        <v>145</v>
-      </c>
-      <c t="s" r="J318" s="7">
-        <v>296</v>
-      </c>
+      <c r="E318" s="7"/>
+      <c r="F318" s="7"/>
+      <c r="G318" s="8"/>
+      <c r="H318" s="8"/>
+      <c r="I318" s="7"/>
+      <c r="J318" s="7"/>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c r="M318" s="7"/>
@@ -11536,97 +11528,117 @@
         <v>13</v>
       </c>
       <c r="B319" s="7">
-        <v>168</v>
+        <v>963</v>
       </c>
       <c t="s" r="C319" s="7">
         <v>14</v>
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="F319" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>297</v>
+        <v>401</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>44</v>
+        <v>271</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
-      <c r="M319" s="7"/>
+      <c t="s" r="M319" s="7">
+        <v>95</v>
+      </c>
     </row>
     <row r="320" ht="15" customHeight="1">
-      <c r="A320" s="6"/>
-      <c r="B320" s="7"/>
-      <c r="C320" s="7"/>
+      <c t="s" r="A320" s="6">
+        <v>13</v>
+      </c>
+      <c r="B320" s="7">
+        <v>403</v>
+      </c>
+      <c t="s" r="C320" s="7">
+        <v>14</v>
+      </c>
       <c r="D320" s="7"/>
-      <c r="E320" s="7"/>
-      <c r="F320" s="7"/>
-      <c r="G320" s="8"/>
-      <c r="H320" s="8"/>
-      <c r="I320" s="7"/>
-      <c r="J320" s="7"/>
+      <c t="s" r="E320" s="7">
+        <v>400</v>
+      </c>
+      <c r="F320" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G320" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H320" s="8">
+        <v>123</v>
+      </c>
+      <c t="s" r="I320" s="7">
+        <v>149</v>
+      </c>
+      <c t="s" r="J320" s="7">
+        <v>99</v>
+      </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
-      <c r="M320" s="7"/>
+      <c t="s" r="M320" s="7">
+        <v>402</v>
+      </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
       <c t="s" r="A321" s="6">
         <v>13</v>
       </c>
       <c r="B321" s="7">
-        <v>963</v>
+        <v>404</v>
       </c>
       <c t="s" r="C321" s="7">
         <v>14</v>
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>397</v>
+        <v>179</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
-      <c t="s" r="M321" s="7">
-        <v>95</v>
-      </c>
+      <c r="M321" s="7"/>
     </row>
     <row r="322" ht="14.25" customHeight="1">
       <c t="s" r="A322" s="6">
         <v>13</v>
       </c>
       <c r="B322" s="7">
-        <v>403</v>
+        <v>465</v>
       </c>
       <c t="s" r="C322" s="7">
         <v>14</v>
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11635,48 +11647,46 @@
         <v>16</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>123</v>
+        <v>270</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>149</v>
+        <v>43</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>99</v>
+        <v>245</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
-      <c t="s" r="M322" s="7">
-        <v>398</v>
-      </c>
+      <c r="M322" s="7"/>
     </row>
     <row r="323" ht="14.25" customHeight="1">
       <c t="s" r="A323" s="6">
         <v>13</v>
       </c>
       <c r="B323" s="7">
-        <v>404</v>
+        <v>466</v>
       </c>
       <c t="s" r="C323" s="7">
         <v>14</v>
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>123</v>
+        <v>270</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>179</v>
+        <v>387</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>259</v>
+        <v>403</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11684,17 +11694,17 @@
     </row>
     <row r="324" ht="14.25" customHeight="1">
       <c t="s" r="A324" s="6">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="B324" s="7">
-        <v>465</v>
+        <v>982</v>
       </c>
       <c t="s" r="C324" s="7">
         <v>14</v>
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11703,83 +11713,67 @@
         <v>16</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>270</v>
+        <v>31</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>43</v>
+        <v>376</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>245</v>
+        <v>208</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c r="M324" s="7"/>
     </row>
     <row r="325" ht="15" customHeight="1">
-      <c t="s" r="A325" s="6">
-        <v>13</v>
-      </c>
-      <c r="B325" s="7">
-        <v>466</v>
-      </c>
-      <c t="s" r="C325" s="7">
-        <v>14</v>
-      </c>
+      <c r="A325" s="6"/>
+      <c r="B325" s="7"/>
+      <c r="C325" s="7"/>
       <c r="D325" s="7"/>
-      <c t="s" r="E325" s="7">
-        <v>396</v>
-      </c>
-      <c r="F325" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G325" s="8">
-        <v>270</v>
-      </c>
-      <c t="s" r="H325" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I325" s="7">
-        <v>385</v>
-      </c>
-      <c t="s" r="J325" s="7">
-        <v>399</v>
-      </c>
+      <c r="E325" s="7"/>
+      <c r="F325" s="7"/>
+      <c r="G325" s="8"/>
+      <c r="H325" s="8"/>
+      <c r="I325" s="7"/>
+      <c r="J325" s="7"/>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c r="M325" s="7"/>
     </row>
     <row r="326" ht="14.25" customHeight="1">
       <c t="s" r="A326" s="6">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="B326" s="7">
-        <v>982</v>
+        <v>125</v>
       </c>
       <c t="s" r="C326" s="7">
         <v>14</v>
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="F326" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
         <v>16</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>374</v>
+        <v>137</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>208</v>
+        <v>249</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
-      <c r="M326" s="7"/>
+      <c t="s" r="M326" s="7">
+        <v>57</v>
+      </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
       <c r="A327" s="6"/>
@@ -11801,64 +11795,84 @@
         <v>13</v>
       </c>
       <c r="B328" s="7">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c t="s" r="C328" s="7">
         <v>14</v>
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>137</v>
+        <v>406</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>249</v>
+        <v>407</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>57</v>
+        <v>408</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
-      <c r="A329" s="6"/>
-      <c r="B329" s="7"/>
-      <c r="C329" s="7"/>
+      <c t="s" r="A329" s="6">
+        <v>13</v>
+      </c>
+      <c r="B329" s="7">
+        <v>129</v>
+      </c>
+      <c t="s" r="C329" s="7">
+        <v>14</v>
+      </c>
       <c r="D329" s="7"/>
-      <c r="E329" s="7"/>
-      <c r="F329" s="7"/>
-      <c r="G329" s="8"/>
-      <c r="H329" s="8"/>
-      <c r="I329" s="7"/>
-      <c r="J329" s="7"/>
+      <c t="s" r="E329" s="7">
+        <v>405</v>
+      </c>
+      <c r="F329" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G329" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H329" s="8">
+        <v>36</v>
+      </c>
+      <c t="s" r="I329" s="7">
+        <v>242</v>
+      </c>
+      <c t="s" r="J329" s="7">
+        <v>196</v>
+      </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
-      <c r="M329" s="7"/>
+      <c t="s" r="M329" s="7">
+        <v>196</v>
+      </c>
     </row>
     <row r="330" ht="15" customHeight="1">
       <c t="s" r="A330" s="6">
         <v>13</v>
       </c>
       <c r="B330" s="7">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c t="s" r="C330" s="7">
         <v>14</v>
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11870,30 +11884,28 @@
         <v>16</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>402</v>
+        <v>87</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>403</v>
+        <v>39</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
-      <c t="s" r="M330" s="7">
-        <v>404</v>
-      </c>
+      <c r="M330" s="7"/>
     </row>
     <row r="331" ht="14.25" customHeight="1">
       <c t="s" r="A331" s="6">
         <v>13</v>
       </c>
       <c r="B331" s="7">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c t="s" r="C331" s="7">
         <v>14</v>
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11905,30 +11917,28 @@
         <v>36</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>196</v>
+        <v>294</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
-      <c t="s" r="M331" s="7">
-        <v>196</v>
-      </c>
+      <c r="M331" s="7"/>
     </row>
     <row r="332" ht="14.25" customHeight="1">
       <c t="s" r="A332" s="6">
         <v>13</v>
       </c>
       <c r="B332" s="7">
-        <v>138</v>
+        <v>376</v>
       </c>
       <c t="s" r="C332" s="7">
         <v>14</v>
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11937,13 +11947,13 @@
         <v>36</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>16</v>
+        <v>409</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>39</v>
+        <v>334</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11954,63 +11964,45 @@
         <v>13</v>
       </c>
       <c r="B333" s="7">
-        <v>147</v>
+        <v>377</v>
       </c>
       <c t="s" r="C333" s="7">
         <v>14</v>
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>16</v>
+        <v>409</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>294</v>
+        <v>152</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c r="M333" s="7"/>
     </row>
     <row r="334" ht="14.25" customHeight="1">
-      <c t="s" r="A334" s="6">
-        <v>13</v>
-      </c>
-      <c r="B334" s="7">
-        <v>376</v>
-      </c>
-      <c t="s" r="C334" s="7">
-        <v>14</v>
-      </c>
+      <c r="A334" s="6"/>
+      <c r="B334" s="7"/>
+      <c r="C334" s="7"/>
       <c r="D334" s="7"/>
-      <c t="s" r="E334" s="7">
-        <v>401</v>
-      </c>
-      <c r="F334" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G334" s="8">
-        <v>36</v>
-      </c>
-      <c t="s" r="H334" s="8">
-        <v>405</v>
-      </c>
-      <c t="s" r="I334" s="7">
-        <v>91</v>
-      </c>
-      <c t="s" r="J334" s="7">
-        <v>333</v>
-      </c>
+      <c r="E334" s="7"/>
+      <c r="F334" s="7"/>
+      <c r="G334" s="8"/>
+      <c r="H334" s="8"/>
+      <c r="I334" s="7"/>
+      <c r="J334" s="7"/>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c r="M334" s="7"/>
@@ -12020,62 +12012,84 @@
         <v>13</v>
       </c>
       <c r="B335" s="7">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c t="s" r="C335" s="7">
         <v>14</v>
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="F335" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>405</v>
+        <v>16</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
-      <c r="M335" s="7"/>
+      <c t="s" r="M335" s="7">
+        <v>411</v>
+      </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
-      <c r="A336" s="6"/>
-      <c r="B336" s="7"/>
-      <c r="C336" s="7"/>
+      <c t="s" r="A336" s="6">
+        <v>13</v>
+      </c>
+      <c r="B336" s="7">
+        <v>402</v>
+      </c>
+      <c t="s" r="C336" s="7">
+        <v>14</v>
+      </c>
       <c r="D336" s="7"/>
-      <c r="E336" s="7"/>
-      <c r="F336" s="7"/>
-      <c r="G336" s="8"/>
-      <c r="H336" s="8"/>
-      <c r="I336" s="7"/>
-      <c r="J336" s="7"/>
+      <c t="s" r="E336" s="7">
+        <v>410</v>
+      </c>
+      <c r="F336" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G336" s="8">
+        <v>123</v>
+      </c>
+      <c t="s" r="H336" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I336" s="7">
+        <v>57</v>
+      </c>
+      <c t="s" r="J336" s="7">
+        <v>50</v>
+      </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
-      <c r="M336" s="7"/>
+      <c t="s" r="M336" s="7">
+        <v>412</v>
+      </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
       <c t="s" r="A337" s="6">
         <v>13</v>
       </c>
       <c r="B337" s="7">
-        <v>401</v>
+        <v>775</v>
       </c>
       <c t="s" r="C337" s="7">
         <v>14</v>
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -12084,68 +12098,64 @@
         <v>16</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>137</v>
+        <v>389</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>140</v>
+        <v>197</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
-      <c t="s" r="M337" s="7">
-        <v>407</v>
-      </c>
+      <c r="M337" s="7"/>
     </row>
     <row r="338" ht="14.25" customHeight="1">
       <c t="s" r="A338" s="6">
         <v>13</v>
       </c>
       <c r="B338" s="7">
-        <v>402</v>
+        <v>772</v>
       </c>
       <c t="s" r="C338" s="7">
         <v>14</v>
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
-      <c t="s" r="M338" s="7">
-        <v>408</v>
-      </c>
+      <c r="M338" s="7"/>
     </row>
     <row r="339" ht="14.25" customHeight="1">
       <c t="s" r="A339" s="6">
         <v>13</v>
       </c>
       <c r="B339" s="7">
-        <v>775</v>
+        <v>495</v>
       </c>
       <c t="s" r="C339" s="7">
         <v>14</v>
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -12154,13 +12164,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>387</v>
+        <v>151</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>197</v>
+        <v>333</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -12171,63 +12181,45 @@
         <v>13</v>
       </c>
       <c r="B340" s="7">
-        <v>772</v>
+        <v>496</v>
       </c>
       <c t="s" r="C340" s="7">
         <v>14</v>
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>158</v>
+        <v>334</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>71</v>
+        <v>315</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c r="M340" s="7"/>
     </row>
     <row r="341" ht="14.25" customHeight="1">
-      <c t="s" r="A341" s="6">
-        <v>13</v>
-      </c>
-      <c r="B341" s="7">
-        <v>495</v>
-      </c>
-      <c t="s" r="C341" s="7">
-        <v>14</v>
-      </c>
+      <c r="A341" s="6"/>
+      <c r="B341" s="7"/>
+      <c r="C341" s="7"/>
       <c r="D341" s="7"/>
-      <c t="s" r="E341" s="7">
-        <v>406</v>
-      </c>
-      <c r="F341" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G341" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H341" s="8">
-        <v>281</v>
-      </c>
-      <c t="s" r="I341" s="7">
-        <v>151</v>
-      </c>
-      <c t="s" r="J341" s="7">
-        <v>332</v>
-      </c>
+      <c r="E341" s="7"/>
+      <c r="F341" s="7"/>
+      <c r="G341" s="8"/>
+      <c r="H341" s="8"/>
+      <c r="I341" s="7"/>
+      <c r="J341" s="7"/>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c r="M341" s="7"/>
@@ -12237,62 +12229,84 @@
         <v>13</v>
       </c>
       <c r="B342" s="7">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c t="s" r="C342" s="7">
         <v>14</v>
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="F342" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>281</v>
+        <v>16</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>333</v>
+        <v>148</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>315</v>
+        <v>149</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
-      <c r="M342" s="7"/>
+      <c t="s" r="M342" s="7">
+        <v>414</v>
+      </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
-      <c r="A343" s="6"/>
-      <c r="B343" s="7"/>
-      <c r="C343" s="7"/>
+      <c t="s" r="A343" s="6">
+        <v>13</v>
+      </c>
+      <c r="B343" s="7">
+        <v>506</v>
+      </c>
+      <c t="s" r="C343" s="7">
+        <v>14</v>
+      </c>
       <c r="D343" s="7"/>
-      <c r="E343" s="7"/>
-      <c r="F343" s="7"/>
-      <c r="G343" s="8"/>
-      <c r="H343" s="8"/>
-      <c r="I343" s="7"/>
-      <c r="J343" s="7"/>
+      <c t="s" r="E343" s="7">
+        <v>413</v>
+      </c>
+      <c r="F343" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G343" s="8">
+        <v>64</v>
+      </c>
+      <c t="s" r="H343" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I343" s="7">
+        <v>196</v>
+      </c>
+      <c t="s" r="J343" s="7">
+        <v>99</v>
+      </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
-      <c r="M343" s="7"/>
+      <c t="s" r="M343" s="7">
+        <v>258</v>
+      </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
       <c t="s" r="A344" s="6">
         <v>13</v>
       </c>
       <c r="B344" s="7">
-        <v>505</v>
+        <v>453</v>
       </c>
       <c t="s" r="C344" s="7">
         <v>14</v>
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12301,68 +12315,64 @@
         <v>16</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>148</v>
+        <v>86</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
-      <c t="s" r="M344" s="7">
-        <v>410</v>
-      </c>
+      <c r="M344" s="7"/>
     </row>
     <row r="345" ht="15" customHeight="1">
       <c t="s" r="A345" s="6">
         <v>13</v>
       </c>
       <c r="B345" s="7">
-        <v>506</v>
+        <v>456</v>
       </c>
       <c t="s" r="C345" s="7">
         <v>14</v>
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>196</v>
+        <v>24</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
-      <c t="s" r="M345" s="7">
-        <v>258</v>
-      </c>
+      <c r="M345" s="7"/>
     </row>
     <row r="346" ht="14.25" customHeight="1">
       <c t="s" r="A346" s="6">
         <v>13</v>
       </c>
       <c r="B346" s="7">
-        <v>453</v>
+        <v>7238</v>
       </c>
       <c t="s" r="C346" s="7">
         <v>14</v>
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12371,13 +12381,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>28</v>
+        <v>286</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>168</v>
+        <v>415</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12385,131 +12395,135 @@
     </row>
     <row r="347" ht="14.25" customHeight="1">
       <c t="s" r="A347" s="6">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="B347" s="7">
-        <v>456</v>
+        <v>7239</v>
       </c>
       <c t="s" r="C347" s="7">
         <v>14</v>
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>28</v>
+        <v>286</v>
       </c>
       <c t="s" r="H347" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>24</v>
+        <v>416</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>26</v>
+        <v>417</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c r="M347" s="7"/>
     </row>
     <row r="348" ht="14.25" customHeight="1">
-      <c t="s" r="A348" s="6">
-        <v>13</v>
-      </c>
-      <c r="B348" s="7">
-        <v>7238</v>
-      </c>
-      <c t="s" r="C348" s="7">
-        <v>14</v>
-      </c>
+      <c r="A348" s="6"/>
+      <c r="B348" s="7"/>
+      <c r="C348" s="7"/>
       <c r="D348" s="7"/>
-      <c t="s" r="E348" s="7">
-        <v>409</v>
-      </c>
-      <c r="F348" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G348" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H348" s="8">
-        <v>286</v>
-      </c>
-      <c t="s" r="I348" s="7">
-        <v>53</v>
-      </c>
-      <c t="s" r="J348" s="7">
-        <v>411</v>
-      </c>
+      <c r="E348" s="7"/>
+      <c r="F348" s="7"/>
+      <c r="G348" s="8"/>
+      <c r="H348" s="8"/>
+      <c r="I348" s="7"/>
+      <c r="J348" s="7"/>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c r="M348" s="7"/>
     </row>
     <row r="349" ht="14.25" customHeight="1">
       <c t="s" r="A349" s="6">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="B349" s="7">
-        <v>7239</v>
+        <v>1382</v>
       </c>
       <c t="s" r="C349" s="7">
         <v>14</v>
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>286</v>
+        <v>36</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>412</v>
+        <v>136</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>413</v>
+        <v>262</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
-      <c r="M349" s="7"/>
+      <c t="s" r="M349" s="7">
+        <v>419</v>
+      </c>
     </row>
     <row r="350" ht="15" customHeight="1">
-      <c r="A350" s="6"/>
-      <c r="B350" s="7"/>
-      <c r="C350" s="7"/>
+      <c t="s" r="A350" s="6">
+        <v>13</v>
+      </c>
+      <c r="B350" s="7">
+        <v>1383</v>
+      </c>
+      <c t="s" r="C350" s="7">
+        <v>14</v>
+      </c>
       <c r="D350" s="7"/>
-      <c r="E350" s="7"/>
-      <c r="F350" s="7"/>
-      <c r="G350" s="8"/>
-      <c r="H350" s="8"/>
-      <c r="I350" s="7"/>
-      <c r="J350" s="7"/>
+      <c t="s" r="E350" s="7">
+        <v>418</v>
+      </c>
+      <c r="F350" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G350" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="H350" s="8">
+        <v>36</v>
+      </c>
+      <c t="s" r="I350" s="7">
+        <v>420</v>
+      </c>
+      <c t="s" r="J350" s="7">
+        <v>222</v>
+      </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
-      <c r="M350" s="7"/>
+      <c t="s" r="M350" s="7">
+        <v>421</v>
+      </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
       <c t="s" r="A351" s="6">
         <v>13</v>
       </c>
       <c r="B351" s="7">
-        <v>1382</v>
+        <v>304</v>
       </c>
       <c t="s" r="C351" s="7">
         <v>14</v>
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12518,18 +12532,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>23</v>
+        <v>230</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>262</v>
+        <v>119</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>415</v>
+        <v>355</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12537,34 +12551,34 @@
         <v>13</v>
       </c>
       <c r="B352" s="7">
-        <v>1383</v>
+        <v>303</v>
       </c>
       <c t="s" r="C352" s="7">
         <v>14</v>
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>23</v>
+        <v>230</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>416</v>
+        <v>65</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>222</v>
+        <v>131</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>417</v>
+        <v>66</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -12572,14 +12586,14 @@
         <v>13</v>
       </c>
       <c r="B353" s="7">
-        <v>304</v>
+        <v>374</v>
       </c>
       <c t="s" r="C353" s="7">
         <v>14</v>
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12588,84 +12602,62 @@
         <v>36</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>230</v>
+        <v>409</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
-      <c t="s" r="M353" s="7">
-        <v>354</v>
-      </c>
+      <c r="M353" s="7"/>
     </row>
     <row r="354" ht="14.25" customHeight="1">
       <c t="s" r="A354" s="6">
         <v>13</v>
       </c>
       <c r="B354" s="7">
-        <v>303</v>
+        <v>375</v>
       </c>
       <c t="s" r="C354" s="7">
         <v>14</v>
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>230</v>
+        <v>409</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>131</v>
+        <v>42</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
-      <c t="s" r="M354" s="7">
-        <v>66</v>
-      </c>
+      <c r="M354" s="7"/>
     </row>
     <row r="355" ht="15" customHeight="1">
-      <c t="s" r="A355" s="6">
-        <v>13</v>
-      </c>
-      <c r="B355" s="7">
-        <v>374</v>
-      </c>
-      <c t="s" r="C355" s="7">
-        <v>14</v>
-      </c>
+      <c r="A355" s="6"/>
+      <c r="B355" s="7"/>
+      <c r="C355" s="7"/>
       <c r="D355" s="7"/>
-      <c t="s" r="E355" s="7">
-        <v>414</v>
-      </c>
-      <c r="F355" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G355" s="8">
-        <v>36</v>
-      </c>
-      <c t="s" r="H355" s="8">
-        <v>405</v>
-      </c>
-      <c t="s" r="I355" s="7">
-        <v>112</v>
-      </c>
-      <c t="s" r="J355" s="7">
-        <v>142</v>
-      </c>
+      <c r="E355" s="7"/>
+      <c r="F355" s="7"/>
+      <c r="G355" s="8"/>
+      <c r="H355" s="8"/>
+      <c r="I355" s="7"/>
+      <c r="J355" s="7"/>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c r="M355" s="7"/>
@@ -12675,62 +12667,84 @@
         <v>13</v>
       </c>
       <c r="B356" s="7">
-        <v>375</v>
+        <v>719</v>
       </c>
       <c t="s" r="C356" s="7">
         <v>14</v>
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="F356" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>405</v>
+        <v>64</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>190</v>
+        <v>420</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
-      <c r="M356" s="7"/>
+      <c t="s" r="M356" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
-      <c r="A357" s="6"/>
-      <c r="B357" s="7"/>
-      <c r="C357" s="7"/>
+      <c t="s" r="A357" s="6">
+        <v>13</v>
+      </c>
+      <c r="B357" s="7">
+        <v>718</v>
+      </c>
+      <c t="s" r="C357" s="7">
+        <v>14</v>
+      </c>
       <c r="D357" s="7"/>
-      <c r="E357" s="7"/>
-      <c r="F357" s="7"/>
-      <c r="G357" s="8"/>
-      <c r="H357" s="8"/>
-      <c r="I357" s="7"/>
-      <c r="J357" s="7"/>
+      <c t="s" r="E357" s="7">
+        <v>422</v>
+      </c>
+      <c r="F357" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G357" s="8">
+        <v>28</v>
+      </c>
+      <c t="s" r="H357" s="8">
+        <v>64</v>
+      </c>
+      <c t="s" r="I357" s="7">
+        <v>47</v>
+      </c>
+      <c t="s" r="J357" s="7">
+        <v>121</v>
+      </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
-      <c r="M357" s="7"/>
+      <c t="s" r="M357" s="7">
+        <v>424</v>
+      </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
       <c t="s" r="A358" s="6">
         <v>13</v>
       </c>
       <c r="B358" s="7">
-        <v>719</v>
+        <v>973</v>
       </c>
       <c t="s" r="C358" s="7">
         <v>14</v>
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12739,83 +12753,79 @@
         <v>64</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>28</v>
+        <v>300</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>416</v>
+        <v>83</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
-      <c t="s" r="M358" s="7">
-        <v>419</v>
-      </c>
+      <c r="M358" s="7"/>
     </row>
     <row r="359" ht="14.25" customHeight="1">
       <c t="s" r="A359" s="6">
         <v>13</v>
       </c>
       <c r="B359" s="7">
-        <v>718</v>
+        <v>814</v>
       </c>
       <c t="s" r="C359" s="7">
         <v>14</v>
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>28</v>
+        <v>300</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>47</v>
+        <v>294</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
-      <c t="s" r="M359" s="7">
-        <v>420</v>
-      </c>
+      <c r="M359" s="7"/>
     </row>
     <row r="360" ht="15" customHeight="1">
       <c t="s" r="A360" s="6">
         <v>13</v>
       </c>
       <c r="B360" s="7">
-        <v>973</v>
+        <v>3908</v>
       </c>
       <c t="s" r="C360" s="7">
         <v>14</v>
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>300</v>
+        <v>378</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>83</v>
+        <v>425</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>126</v>
+        <v>426</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12823,114 +12833,116 @@
     </row>
     <row r="361" ht="14.25" customHeight="1">
       <c t="s" r="A361" s="6">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="B361" s="7">
-        <v>814</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>300</v>
+        <v>378</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>294</v>
+        <v>427</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>61</v>
+        <v>428</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c r="M361" s="7"/>
     </row>
     <row r="362" ht="14.25" customHeight="1">
-      <c t="s" r="A362" s="6">
-        <v>13</v>
-      </c>
-      <c r="B362" s="7">
-        <v>3908</v>
-      </c>
-      <c t="s" r="C362" s="7">
-        <v>14</v>
-      </c>
+      <c r="A362" s="6"/>
+      <c r="B362" s="7"/>
+      <c r="C362" s="7"/>
       <c r="D362" s="7"/>
-      <c t="s" r="E362" s="7">
-        <v>418</v>
-      </c>
-      <c r="F362" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G362" s="8">
-        <v>36</v>
-      </c>
-      <c t="s" r="H362" s="8">
-        <v>376</v>
-      </c>
-      <c t="s" r="I362" s="7">
-        <v>421</v>
-      </c>
-      <c t="s" r="J362" s="7">
-        <v>422</v>
-      </c>
+      <c r="E362" s="7"/>
+      <c r="F362" s="7"/>
+      <c r="G362" s="8"/>
+      <c r="H362" s="8"/>
+      <c r="I362" s="7"/>
+      <c r="J362" s="7"/>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c r="M362" s="7"/>
     </row>
     <row r="363" ht="14.25" customHeight="1">
       <c t="s" r="A363" s="6">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="B363" s="7">
-        <v>3909</v>
+        <v>925</v>
       </c>
       <c t="s" r="C363" s="7">
         <v>14</v>
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>376</v>
+        <v>35</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>424</v>
+        <v>354</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
-      <c r="M363" s="7"/>
+      <c t="s" r="M363" s="7">
+        <v>338</v>
+      </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
-      <c r="A364" s="6"/>
-      <c r="B364" s="7"/>
-      <c r="C364" s="7"/>
+      <c t="s" r="A364" s="6">
+        <v>13</v>
+      </c>
+      <c r="B364" s="7">
+        <v>275</v>
+      </c>
+      <c t="s" r="C364" s="7">
+        <v>14</v>
+      </c>
       <c r="D364" s="7"/>
-      <c r="E364" s="7"/>
-      <c r="F364" s="7"/>
-      <c r="G364" s="8"/>
-      <c r="H364" s="8"/>
-      <c r="I364" s="7"/>
-      <c r="J364" s="7"/>
+      <c t="s" r="E364" s="7">
+        <v>429</v>
+      </c>
+      <c r="F364" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G364" s="8">
+        <v>88</v>
+      </c>
+      <c t="s" r="H364" s="8">
+        <v>36</v>
+      </c>
+      <c t="s" r="I364" s="7">
+        <v>179</v>
+      </c>
+      <c t="s" r="J364" s="7">
+        <v>190</v>
+      </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c r="M364" s="7"/>
@@ -12940,49 +12952,47 @@
         <v>13</v>
       </c>
       <c r="B365" s="7">
-        <v>925</v>
+        <v>280</v>
       </c>
       <c t="s" r="C365" s="7">
         <v>14</v>
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>88</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>416</v>
+        <v>143</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
-      <c t="s" r="M365" s="7">
-        <v>337</v>
-      </c>
+      <c r="M365" s="7"/>
     </row>
     <row r="366" ht="14.25" customHeight="1">
       <c t="s" r="A366" s="6">
         <v>13</v>
       </c>
       <c r="B366" s="7">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c t="s" r="C366" s="7">
         <v>14</v>
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12994,44 +13004,26 @@
         <v>36</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>190</v>
+        <v>144</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c r="M366" s="7"/>
     </row>
     <row r="367" ht="14.25" customHeight="1">
-      <c t="s" r="A367" s="6">
-        <v>13</v>
-      </c>
-      <c r="B367" s="7">
-        <v>280</v>
-      </c>
-      <c t="s" r="C367" s="7">
-        <v>14</v>
-      </c>
+      <c r="A367" s="6"/>
+      <c r="B367" s="7"/>
+      <c r="C367" s="7"/>
       <c r="D367" s="7"/>
-      <c t="s" r="E367" s="7">
-        <v>425</v>
-      </c>
-      <c r="F367" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G367" s="8">
-        <v>36</v>
-      </c>
-      <c t="s" r="H367" s="8">
-        <v>88</v>
-      </c>
-      <c t="s" r="I367" s="7">
-        <v>143</v>
-      </c>
-      <c t="s" r="J367" s="7">
-        <v>343</v>
-      </c>
+      <c r="E367" s="7"/>
+      <c r="F367" s="7"/>
+      <c r="G367" s="8"/>
+      <c r="H367" s="8"/>
+      <c r="I367" s="7"/>
+      <c r="J367" s="7"/>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c r="M367" s="7"/>
@@ -13041,62 +13033,84 @@
         <v>13</v>
       </c>
       <c r="B368" s="7">
-        <v>281</v>
+        <v>501</v>
       </c>
       <c t="s" r="C368" s="7">
         <v>14</v>
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>213</v>
+        <v>431</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
-      <c r="M368" s="7"/>
+      <c t="s" r="M368" s="7">
+        <v>432</v>
+      </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
-      <c r="A369" s="6"/>
-      <c r="B369" s="7"/>
-      <c r="C369" s="7"/>
+      <c t="s" r="A369" s="6">
+        <v>13</v>
+      </c>
+      <c r="B369" s="7">
+        <v>514</v>
+      </c>
+      <c t="s" r="C369" s="7">
+        <v>14</v>
+      </c>
       <c r="D369" s="7"/>
-      <c r="E369" s="7"/>
-      <c r="F369" s="7"/>
-      <c r="G369" s="8"/>
-      <c r="H369" s="8"/>
-      <c r="I369" s="7"/>
-      <c r="J369" s="7"/>
+      <c t="s" r="E369" s="7">
+        <v>430</v>
+      </c>
+      <c r="F369" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G369" s="8">
+        <v>64</v>
+      </c>
+      <c t="s" r="H369" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I369" s="7">
+        <v>139</v>
+      </c>
+      <c t="s" r="J369" s="7">
+        <v>140</v>
+      </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
-      <c r="M369" s="7"/>
+      <c t="s" r="M369" s="7">
+        <v>433</v>
+      </c>
     </row>
     <row r="370" ht="15" customHeight="1">
       <c t="s" r="A370" s="6">
         <v>13</v>
       </c>
       <c r="B370" s="7">
-        <v>501</v>
+        <v>563</v>
       </c>
       <c t="s" r="C370" s="7">
         <v>14</v>
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13105,18 +13119,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>64</v>
+        <v>230</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>427</v>
+        <v>57</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>137</v>
+        <v>224</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13124,34 +13138,34 @@
         <v>13</v>
       </c>
       <c r="B371" s="7">
-        <v>514</v>
+        <v>564</v>
       </c>
       <c t="s" r="C371" s="7">
         <v>14</v>
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>64</v>
+        <v>230</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>139</v>
+        <v>265</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13159,14 +13173,14 @@
         <v>13</v>
       </c>
       <c r="B372" s="7">
-        <v>563</v>
+        <v>948</v>
       </c>
       <c t="s" r="C372" s="7">
         <v>14</v>
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13175,48 +13189,46 @@
         <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>230</v>
+        <v>436</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>224</v>
+        <v>43</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
-      <c t="s" r="M372" s="7">
-        <v>430</v>
-      </c>
+      <c r="M372" s="7"/>
     </row>
     <row r="373" ht="14.25" customHeight="1">
       <c t="s" r="A373" s="6">
         <v>13</v>
       </c>
       <c r="B373" s="7">
-        <v>564</v>
+        <v>949</v>
       </c>
       <c t="s" r="C373" s="7">
         <v>14</v>
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>230</v>
+        <v>436</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>265</v>
+        <v>60</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13227,14 +13239,14 @@
         <v>13</v>
       </c>
       <c r="B374" s="7">
-        <v>948</v>
+        <v>962</v>
       </c>
       <c t="s" r="C374" s="7">
         <v>14</v>
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13243,47 +13255,29 @@
         <v>16</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>431</v>
+        <v>35</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>274</v>
+        <v>437</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>43</v>
+        <v>327</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c r="M374" s="7"/>
     </row>
     <row r="375" ht="15" customHeight="1">
-      <c t="s" r="A375" s="6">
-        <v>13</v>
-      </c>
-      <c r="B375" s="7">
-        <v>949</v>
-      </c>
-      <c t="s" r="C375" s="7">
-        <v>14</v>
-      </c>
+      <c r="A375" s="6"/>
+      <c r="B375" s="7"/>
+      <c r="C375" s="7"/>
       <c r="D375" s="7"/>
-      <c t="s" r="E375" s="7">
-        <v>426</v>
-      </c>
-      <c r="F375" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G375" s="8">
-        <v>431</v>
-      </c>
-      <c t="s" r="H375" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I375" s="7">
-        <v>60</v>
-      </c>
-      <c t="s" r="J375" s="7">
-        <v>144</v>
-      </c>
+      <c r="E375" s="7"/>
+      <c r="F375" s="7"/>
+      <c r="G375" s="8"/>
+      <c r="H375" s="8"/>
+      <c r="I375" s="7"/>
+      <c r="J375" s="7"/>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c r="M375" s="7"/>
@@ -13293,148 +13287,148 @@
         <v>13</v>
       </c>
       <c r="B376" s="7">
-        <v>962</v>
+        <v>813</v>
       </c>
       <c t="s" r="C376" s="7">
         <v>14</v>
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>35</v>
+        <v>300</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>432</v>
+        <v>208</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>327</v>
+        <v>119</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
-      <c r="M376" s="7"/>
+      <c t="s" r="M376" s="7">
+        <v>96</v>
+      </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
-      <c r="A377" s="6"/>
-      <c r="B377" s="7"/>
-      <c r="C377" s="7"/>
+      <c t="s" r="A377" s="6">
+        <v>13</v>
+      </c>
+      <c r="B377" s="7">
+        <v>970</v>
+      </c>
+      <c t="s" r="C377" s="7">
+        <v>14</v>
+      </c>
       <c r="D377" s="7"/>
-      <c r="E377" s="7"/>
-      <c r="F377" s="7"/>
-      <c r="G377" s="8"/>
-      <c r="H377" s="8"/>
-      <c r="I377" s="7"/>
-      <c r="J377" s="7"/>
+      <c t="s" r="E377" s="7">
+        <v>438</v>
+      </c>
+      <c r="F377" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G377" s="8">
+        <v>300</v>
+      </c>
+      <c t="s" r="H377" s="8">
+        <v>64</v>
+      </c>
+      <c t="s" r="I377" s="7">
+        <v>310</v>
+      </c>
+      <c t="s" r="J377" s="7">
+        <v>83</v>
+      </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
-      <c r="M377" s="7"/>
+      <c t="s" r="M377" s="7">
+        <v>439</v>
+      </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
       <c t="s" r="A378" s="6">
         <v>13</v>
       </c>
       <c r="B378" s="7">
-        <v>813</v>
+        <v>715</v>
       </c>
       <c t="s" r="C378" s="7">
         <v>14</v>
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>300</v>
+        <v>28</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>208</v>
+        <v>133</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
-      <c t="s" r="M378" s="7">
-        <v>96</v>
-      </c>
+      <c r="M378" s="7"/>
     </row>
     <row r="379" ht="14.25" customHeight="1">
       <c t="s" r="A379" s="6">
         <v>13</v>
       </c>
       <c r="B379" s="7">
-        <v>970</v>
+        <v>714</v>
       </c>
       <c t="s" r="C379" s="7">
         <v>14</v>
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>300</v>
+        <v>28</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
-      <c t="s" r="M379" s="7">
-        <v>434</v>
-      </c>
+      <c r="M379" s="7"/>
     </row>
     <row r="380" ht="15" customHeight="1">
-      <c t="s" r="A380" s="6">
-        <v>13</v>
-      </c>
-      <c r="B380" s="7">
-        <v>715</v>
-      </c>
-      <c t="s" r="C380" s="7">
-        <v>14</v>
-      </c>
+      <c r="A380" s="6"/>
+      <c r="B380" s="7"/>
+      <c r="C380" s="7"/>
       <c r="D380" s="7"/>
-      <c t="s" r="E380" s="7">
-        <v>433</v>
-      </c>
-      <c r="F380" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G380" s="8">
-        <v>64</v>
-      </c>
-      <c t="s" r="H380" s="8">
-        <v>28</v>
-      </c>
-      <c t="s" r="I380" s="7">
-        <v>133</v>
-      </c>
-      <c t="s" r="J380" s="7">
-        <v>71</v>
-      </c>
+      <c r="E380" s="7"/>
+      <c r="F380" s="7"/>
+      <c r="G380" s="8"/>
+      <c r="H380" s="8"/>
+      <c r="I380" s="7"/>
+      <c r="J380" s="7"/>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c r="M380" s="7"/>
@@ -13444,62 +13438,84 @@
         <v>13</v>
       </c>
       <c r="B381" s="7">
-        <v>714</v>
+        <v>270</v>
       </c>
       <c t="s" r="C381" s="7">
         <v>14</v>
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
-      <c r="M381" s="7"/>
+      <c t="s" r="M381" s="7">
+        <v>441</v>
+      </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
-      <c r="A382" s="6"/>
-      <c r="B382" s="7"/>
-      <c r="C382" s="7"/>
+      <c t="s" r="A382" s="6">
+        <v>13</v>
+      </c>
+      <c r="B382" s="7">
+        <v>271</v>
+      </c>
+      <c t="s" r="C382" s="7">
+        <v>14</v>
+      </c>
       <c r="D382" s="7"/>
-      <c r="E382" s="7"/>
-      <c r="F382" s="7"/>
-      <c r="G382" s="8"/>
-      <c r="H382" s="8"/>
-      <c r="I382" s="7"/>
-      <c r="J382" s="7"/>
+      <c t="s" r="E382" s="7">
+        <v>440</v>
+      </c>
+      <c r="F382" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G382" s="8">
+        <v>88</v>
+      </c>
+      <c t="s" r="H382" s="8">
+        <v>36</v>
+      </c>
+      <c t="s" r="I382" s="7">
+        <v>217</v>
+      </c>
+      <c t="s" r="J382" s="7">
+        <v>360</v>
+      </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
-      <c r="M382" s="7"/>
+      <c t="s" r="M382" s="7">
+        <v>187</v>
+      </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
       <c t="s" r="A383" s="6">
         <v>13</v>
       </c>
       <c r="B383" s="7">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c t="s" r="C383" s="7">
         <v>14</v>
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13508,18 +13524,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>88</v>
+        <v>230</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>327</v>
+        <v>156</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>139</v>
+        <v>251</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -13527,49 +13543,47 @@
         <v>13</v>
       </c>
       <c r="B384" s="7">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c t="s" r="C384" s="7">
         <v>14</v>
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>88</v>
+        <v>230</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>217</v>
+        <v>263</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>358</v>
+        <v>311</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
-      <c t="s" r="M384" s="7">
-        <v>187</v>
-      </c>
+      <c r="M384" s="7"/>
     </row>
     <row r="385" ht="15" customHeight="1">
       <c t="s" r="A385" s="6">
         <v>13</v>
       </c>
       <c r="B385" s="7">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c t="s" r="C385" s="7">
         <v>14</v>
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13578,48 +13592,46 @@
         <v>36</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>230</v>
+        <v>28</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>251</v>
+        <v>101</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
-      <c t="s" r="M385" s="7">
-        <v>437</v>
-      </c>
+      <c r="M385" s="7"/>
     </row>
     <row r="386" ht="14.25" customHeight="1">
       <c t="s" r="A386" s="6">
         <v>13</v>
       </c>
       <c r="B386" s="7">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c t="s" r="C386" s="7">
         <v>14</v>
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>230</v>
+        <v>28</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>263</v>
+        <v>90</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>311</v>
+        <v>151</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13630,14 +13642,14 @@
         <v>13</v>
       </c>
       <c r="B387" s="7">
-        <v>327</v>
+        <v>642</v>
       </c>
       <c t="s" r="C387" s="7">
         <v>14</v>
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13646,13 +13658,13 @@
         <v>36</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13663,29 +13675,29 @@
         <v>13</v>
       </c>
       <c r="B388" s="7">
-        <v>326</v>
+        <v>643</v>
       </c>
       <c t="s" r="C388" s="7">
         <v>14</v>
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>90</v>
+        <v>215</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>151</v>
+        <v>443</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13696,14 +13708,14 @@
         <v>13</v>
       </c>
       <c r="B389" s="7">
-        <v>642</v>
+        <v>162</v>
       </c>
       <c t="s" r="C389" s="7">
         <v>14</v>
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13712,47 +13724,29 @@
         <v>36</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>301</v>
+        <v>106</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>144</v>
+        <v>444</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c r="M389" s="7"/>
     </row>
     <row r="390" ht="15" customHeight="1">
-      <c t="s" r="A390" s="6">
-        <v>13</v>
-      </c>
-      <c r="B390" s="7">
-        <v>643</v>
-      </c>
-      <c t="s" r="C390" s="7">
-        <v>14</v>
-      </c>
+      <c r="A390" s="6"/>
+      <c r="B390" s="7"/>
+      <c r="C390" s="7"/>
       <c r="D390" s="7"/>
-      <c t="s" r="E390" s="7">
-        <v>435</v>
-      </c>
-      <c r="F390" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G390" s="8">
-        <v>64</v>
-      </c>
-      <c t="s" r="H390" s="8">
-        <v>36</v>
-      </c>
-      <c t="s" r="I390" s="7">
-        <v>215</v>
-      </c>
-      <c t="s" r="J390" s="7">
-        <v>438</v>
-      </c>
+      <c r="E390" s="7"/>
+      <c r="F390" s="7"/>
+      <c r="G390" s="8"/>
+      <c r="H390" s="8"/>
+      <c r="I390" s="7"/>
+      <c r="J390" s="7"/>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c r="M390" s="7"/>
@@ -13762,29 +13756,29 @@
         <v>13</v>
       </c>
       <c r="B391" s="7">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c t="s" r="C391" s="7">
-        <v>14</v>
+        <v>445</v>
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="F391" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>36</v>
+        <v>260</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>439</v>
+        <v>215</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13810,62 +13804,82 @@
         <v>13</v>
       </c>
       <c r="B393" s="7">
-        <v>24</v>
+        <v>934</v>
       </c>
       <c t="s" r="C393" s="7">
-        <v>440</v>
+        <v>14</v>
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="F393" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>260</v>
+        <v>16</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>16</v>
+        <v>210</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>215</v>
+        <v>124</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
-      <c r="M393" s="7"/>
+      <c t="s" r="M393" s="7">
+        <v>448</v>
+      </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
-      <c r="A394" s="6"/>
-      <c r="B394" s="7"/>
-      <c r="C394" s="7"/>
+      <c t="s" r="A394" s="6">
+        <v>13</v>
+      </c>
+      <c r="B394" s="7">
+        <v>935</v>
+      </c>
+      <c t="s" r="C394" s="7">
+        <v>14</v>
+      </c>
       <c r="D394" s="7"/>
-      <c r="E394" s="7"/>
-      <c r="F394" s="7"/>
-      <c r="G394" s="8"/>
-      <c r="H394" s="8"/>
-      <c r="I394" s="7"/>
-      <c r="J394" s="7"/>
+      <c t="s" r="E394" s="7">
+        <v>447</v>
+      </c>
+      <c r="F394" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G394" s="8">
+        <v>210</v>
+      </c>
+      <c t="s" r="H394" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I394" s="7">
+        <v>331</v>
+      </c>
+      <c t="s" r="J394" s="7">
+        <v>29</v>
+      </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c r="M394" s="7"/>
     </row>
     <row r="395" ht="15" customHeight="1">
       <c t="s" r="A395" s="6">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="B395" s="7">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c t="s" r="C395" s="7">
         <v>14</v>
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13877,111 +13891,113 @@
         <v>210</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>124</v>
+        <v>217</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
-      <c t="s" r="M395" s="7">
-        <v>443</v>
-      </c>
+      <c r="M395" s="7"/>
     </row>
     <row r="396" ht="14.25" customHeight="1">
-      <c t="s" r="A396" s="6">
-        <v>13</v>
-      </c>
-      <c r="B396" s="7">
-        <v>935</v>
-      </c>
-      <c t="s" r="C396" s="7">
-        <v>14</v>
-      </c>
+      <c r="A396" s="6"/>
+      <c r="B396" s="7"/>
+      <c r="C396" s="7"/>
       <c r="D396" s="7"/>
-      <c t="s" r="E396" s="7">
-        <v>442</v>
-      </c>
-      <c r="F396" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G396" s="8">
-        <v>210</v>
-      </c>
-      <c t="s" r="H396" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I396" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="J396" s="7">
-        <v>29</v>
-      </c>
+      <c r="E396" s="7"/>
+      <c r="F396" s="7"/>
+      <c r="G396" s="8"/>
+      <c r="H396" s="8"/>
+      <c r="I396" s="7"/>
+      <c r="J396" s="7"/>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c r="M396" s="7"/>
     </row>
     <row r="397" ht="14.25" customHeight="1">
       <c t="s" r="A397" s="6">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="B397" s="7">
-        <v>932</v>
+        <v>1242</v>
       </c>
       <c t="s" r="C397" s="7">
         <v>14</v>
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>54</v>
+        <v>279</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
-      <c r="M397" s="7"/>
+      <c t="s" r="M397" s="7">
+        <v>272</v>
+      </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
-      <c r="A398" s="6"/>
-      <c r="B398" s="7"/>
-      <c r="C398" s="7"/>
+      <c t="s" r="A398" s="6">
+        <v>13</v>
+      </c>
+      <c r="B398" s="7">
+        <v>1241</v>
+      </c>
+      <c t="s" r="C398" s="7">
+        <v>14</v>
+      </c>
       <c r="D398" s="7"/>
-      <c r="E398" s="7"/>
-      <c r="F398" s="7"/>
-      <c r="G398" s="8"/>
-      <c r="H398" s="8"/>
-      <c r="I398" s="7"/>
-      <c r="J398" s="7"/>
+      <c t="s" r="E398" s="7">
+        <v>449</v>
+      </c>
+      <c r="F398" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G398" s="8">
+        <v>178</v>
+      </c>
+      <c t="s" r="H398" s="8">
+        <v>36</v>
+      </c>
+      <c t="s" r="I398" s="7">
+        <v>57</v>
+      </c>
+      <c t="s" r="J398" s="7">
+        <v>121</v>
+      </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
-      <c r="M398" s="7"/>
+      <c t="s" r="M398" s="7">
+        <v>310</v>
+      </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
       <c t="s" r="A399" s="6">
         <v>13</v>
       </c>
       <c r="B399" s="7">
-        <v>1242</v>
+        <v>852</v>
       </c>
       <c t="s" r="C399" s="7">
         <v>14</v>
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -13990,18 +14006,20 @@
         <v>36</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>178</v>
+        <v>436</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>279</v>
+        <v>187</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>140</v>
-      </c>
-      <c r="K399" s="7"/>
+        <v>293</v>
+      </c>
+      <c t="s" r="K399" s="7">
+        <v>131</v>
+      </c>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>272</v>
+        <v>331</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14009,153 +14027,151 @@
         <v>13</v>
       </c>
       <c r="B400" s="7">
-        <v>1241</v>
+        <v>853</v>
       </c>
       <c t="s" r="C400" s="7">
         <v>14</v>
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>178</v>
+        <v>436</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>57</v>
+        <v>124</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>121</v>
-      </c>
-      <c r="K400" s="7"/>
+        <v>60</v>
+      </c>
+      <c t="s" r="K400" s="7">
+        <v>25</v>
+      </c>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>310</v>
+        <v>334</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
-      <c t="s" r="A401" s="6">
-        <v>13</v>
-      </c>
-      <c r="B401" s="7">
-        <v>852</v>
-      </c>
-      <c t="s" r="C401" s="7">
-        <v>14</v>
-      </c>
+      <c r="A401" s="6"/>
+      <c r="B401" s="7"/>
+      <c r="C401" s="7"/>
       <c r="D401" s="7"/>
-      <c t="s" r="E401" s="7">
-        <v>444</v>
-      </c>
-      <c r="F401" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G401" s="8">
-        <v>36</v>
-      </c>
-      <c t="s" r="H401" s="8">
-        <v>431</v>
-      </c>
-      <c t="s" r="I401" s="7">
-        <v>187</v>
-      </c>
-      <c t="s" r="J401" s="7">
-        <v>293</v>
-      </c>
-      <c t="s" r="K401" s="7">
-        <v>131</v>
-      </c>
+      <c r="E401" s="7"/>
+      <c r="F401" s="7"/>
+      <c r="G401" s="8"/>
+      <c r="H401" s="8"/>
+      <c r="I401" s="7"/>
+      <c r="J401" s="7"/>
+      <c r="K401" s="7"/>
       <c r="L401" s="7"/>
-      <c t="s" r="M401" s="7">
-        <v>330</v>
-      </c>
+      <c r="M401" s="7"/>
     </row>
     <row r="402" ht="14.25" customHeight="1">
       <c t="s" r="A402" s="6">
         <v>13</v>
       </c>
       <c r="B402" s="7">
-        <v>853</v>
+        <v>137</v>
       </c>
       <c t="s" r="C402" s="7">
         <v>14</v>
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="F402" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>431</v>
+        <v>16</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>60</v>
-      </c>
-      <c t="s" r="K402" s="7">
-        <v>25</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="K402" s="7"/>
       <c r="L402" s="7"/>
-      <c t="s" r="M402" s="7">
-        <v>333</v>
-      </c>
+      <c r="M402" s="7"/>
     </row>
     <row r="403" ht="14.25" customHeight="1">
-      <c r="A403" s="6"/>
-      <c r="B403" s="7"/>
-      <c r="C403" s="7"/>
+      <c t="s" r="A403" s="6">
+        <v>13</v>
+      </c>
+      <c r="B403" s="7">
+        <v>640</v>
+      </c>
+      <c t="s" r="C403" s="7">
+        <v>14</v>
+      </c>
       <c r="D403" s="7"/>
-      <c r="E403" s="7"/>
-      <c r="F403" s="7"/>
-      <c r="G403" s="8"/>
-      <c r="H403" s="8"/>
-      <c r="I403" s="7"/>
-      <c r="J403" s="7"/>
-      <c r="K403" s="7"/>
+      <c t="s" r="E403" s="7">
+        <v>450</v>
+      </c>
+      <c r="F403" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G403" s="8">
+        <v>36</v>
+      </c>
+      <c t="s" r="H403" s="8">
+        <v>64</v>
+      </c>
+      <c t="s" r="I403" s="7">
+        <v>314</v>
+      </c>
+      <c t="s" r="J403" s="7">
+        <v>331</v>
+      </c>
+      <c t="s" r="K403" s="7">
+        <v>41</v>
+      </c>
       <c r="L403" s="7"/>
-      <c r="M403" s="7"/>
+      <c t="s" r="M403" s="7">
+        <v>236</v>
+      </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
       <c t="s" r="A404" s="6">
         <v>13</v>
       </c>
       <c r="B404" s="7">
-        <v>143</v>
+        <v>639</v>
       </c>
       <c t="s" r="C404" s="7">
         <v>14</v>
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F404" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>158</v>
+        <v>25</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>182</v>
+        <v>451</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -14166,14 +14182,14 @@
         <v>13</v>
       </c>
       <c r="B405" s="7">
-        <v>146</v>
+        <v>644</v>
       </c>
       <c t="s" r="C405" s="7">
         <v>14</v>
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
@@ -14182,13 +14198,13 @@
         <v>36</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14199,29 +14215,29 @@
         <v>13</v>
       </c>
       <c r="B406" s="7">
-        <v>1127</v>
+        <v>645</v>
       </c>
       <c t="s" r="C406" s="7">
         <v>14</v>
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>446</v>
+        <v>145</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>226</v>
+        <v>296</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14232,14 +14248,14 @@
         <v>13</v>
       </c>
       <c r="B407" s="7">
-        <v>1128</v>
+        <v>168</v>
       </c>
       <c t="s" r="C407" s="7">
         <v>14</v>
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
@@ -14251,10 +14267,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>447</v>
+        <v>297</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>448</v>
+        <v>44</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14287,13 +14303,13 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>36</v>
@@ -14322,7 +14338,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
@@ -14340,11 +14356,11 @@
         <v>160</v>
       </c>
       <c t="s" r="K410" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>395</v>
+        <v>451</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -14359,7 +14375,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
@@ -14368,7 +14384,7 @@
         <v>82</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c t="s" r="I411" s="7">
         <v>245</v>
@@ -14377,11 +14393,11 @@
         <v>319</v>
       </c>
       <c t="s" r="K411" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -14407,11 +14423,11 @@
         <v>606</v>
       </c>
       <c t="s" r="C413" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -14446,7 +14462,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -14455,7 +14471,7 @@
         <v>82</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="I414" s="7">
         <v>217</v>
@@ -14481,13 +14497,13 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>82</v>
@@ -14496,7 +14512,7 @@
         <v>294</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14529,7 +14545,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14549,7 +14565,7 @@
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -14575,23 +14591,23 @@
         <v>35</v>
       </c>
       <c t="s" r="C419" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>319</v>
@@ -14627,7 +14643,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -14636,7 +14652,7 @@
         <v>82</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c t="s" r="I421" s="7">
         <v>309</v>
@@ -14662,13 +14678,13 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>82</v>
@@ -14677,7 +14693,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14710,7 +14726,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F424" s="7">
         <v>330</v>
@@ -14722,7 +14738,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>144</v>
@@ -14739,11 +14755,11 @@
         <v>32</v>
       </c>
       <c t="s" r="C425" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F425" s="7">
         <v>330</v>
@@ -14752,13 +14768,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c t="s" r="I425" s="7">
         <v>297</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14791,7 +14807,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F427" s="7">
         <v>330</v>
@@ -14800,7 +14816,7 @@
         <v>36</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c t="s" r="I427" s="7">
         <v>50</v>
@@ -14810,7 +14826,9 @@
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
-      <c r="M427" s="7"/>
+      <c t="s" r="M427" s="7">
+        <v>470</v>
+      </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
       <c t="s" r="A428" s="6">
@@ -14824,22 +14842,22 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F428" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14872,7 +14890,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -14881,7 +14899,7 @@
         <v>36</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c t="s" r="I430" s="7">
         <v>119</v>
@@ -14892,7 +14910,7 @@
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -14907,19 +14925,19 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c t="s" r="J431" s="7">
         <v>278</v>
@@ -14930,7 +14948,7 @@
     </row>
     <row r="432" ht="15.75" customHeight="1">
       <c t="s" r="A432" s="9">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B432" s="9"/>
       <c r="C432" s="9"/>
@@ -14950,7 +14968,7 @@
     <row r="433" ht="65.25" customHeight="1"/>
     <row r="434" ht="16.5" customHeight="1">
       <c t="s" r="A434" s="10">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B434" s="10"/>
       <c r="C434" s="10"/>
@@ -14963,7 +14981,7 @@
       <c r="J434" s="10"/>
       <c r="K434" s="10"/>
       <c t="s" r="L434" s="11">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="M434" s="11"/>
       <c r="N434" s="11"/>
